--- a/NHIS variable list REVISED 6-14-24_Now_Moddified new.xlsx
+++ b/NHIS variable list REVISED 6-14-24_Now_Moddified new.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ncaandt-my.sharepoint.com/personal/hmoradi_ncat_edu/Documents/06_Codes/NHIS-surf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{1CD7837E-75C9-5E40-80AC-B4DD76B197DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3AAB2450-3649-4FEB-87C7-B4C89B91F874}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{1CD7837E-75C9-5E40-80AC-B4DD76B197DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B7E2BCA-6C1E-4F1F-B0E5-E75077A43D0E}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AA949552-4F9F-40F0-90AF-3F34A678AD64}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AA949552-4F9F-40F0-90AF-3F34A678AD64}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -255,9 +255,6 @@
     <t>how often feel worried, nervous, or anxious</t>
   </si>
   <si>
-    <t>take medicaiton for worried/nervous/anxious feelings</t>
-  </si>
-  <si>
     <t>level of feelings when last felt worried/nervous/anxious</t>
   </si>
   <si>
@@ -781,6 +778,9 @@
   </si>
   <si>
     <t>Age</t>
+  </si>
+  <si>
+    <t>take medication for worried/nervous/anxious feelings</t>
   </si>
 </sst>
 </file>
@@ -1261,14 +1261,14 @@
     <col min="2" max="2" width="23.140625" customWidth="1"/>
     <col min="3" max="3" width="46.42578125" customWidth="1"/>
     <col min="4" max="4" width="41.42578125" style="8" customWidth="1"/>
-    <col min="5" max="5" width="66" style="11" customWidth="1"/>
+    <col min="5" max="5" width="110" style="11" customWidth="1"/>
     <col min="6" max="6" width="69.7109375" style="11" customWidth="1"/>
     <col min="10" max="10" width="23.28515625" style="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B1" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C1" s="7" t="s">
         <v>0</v>
@@ -1277,13 +1277,13 @@
         <v>1</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J1" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="2" spans="2:10" x14ac:dyDescent="0.25">
@@ -1294,13 +1294,13 @@
         <v>3</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E2" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="F2" s="11" t="s">
         <v>132</v>
-      </c>
-      <c r="F2" s="11" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.25">
@@ -1311,16 +1311,16 @@
         <v>5</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E3" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="F3" s="11" t="s">
         <v>249</v>
       </c>
-      <c r="F3" s="11" t="s">
-        <v>250</v>
-      </c>
       <c r="J3" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.25">
@@ -1331,13 +1331,13 @@
         <v>15</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.25">
@@ -1348,107 +1348,107 @@
         <v>21</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E5" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="F5" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="F5" s="11" t="s">
-        <v>137</v>
-      </c>
       <c r="J5" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B6" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E7" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="F7" s="12" t="s">
         <v>235</v>
       </c>
-      <c r="F7" s="12" t="s">
-        <v>236</v>
-      </c>
       <c r="J7" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B8" s="16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F8" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="J8" s="12" t="s">
         <v>237</v>
-      </c>
-      <c r="J8" s="12" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="16" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.25">
@@ -1459,16 +1459,16 @@
         <v>17</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.25">
@@ -1479,16 +1479,16 @@
         <v>25</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.25">
@@ -1499,16 +1499,16 @@
         <v>27</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.25">
@@ -1519,16 +1519,16 @@
         <v>29</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.25">
@@ -1539,13 +1539,13 @@
         <v>75</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E15" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="F15" s="11" t="s">
         <v>145</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.25">
@@ -1553,19 +1553,19 @@
         <v>73</v>
       </c>
       <c r="C16" t="s">
-        <v>76</v>
+        <v>251</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E16" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="F16" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="F16" s="11" t="s">
-        <v>148</v>
-      </c>
       <c r="J16" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.25">
@@ -1573,124 +1573,124 @@
         <v>74</v>
       </c>
       <c r="C17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C19" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J19" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="C21" t="s">
         <v>88</v>
       </c>
-      <c r="C21" t="s">
-        <v>89</v>
-      </c>
       <c r="D21" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22" t="s">
         <v>90</v>
       </c>
-      <c r="C22" t="s">
-        <v>91</v>
-      </c>
       <c r="D22" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E22" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="F22" s="11" t="s">
         <v>155</v>
-      </c>
-      <c r="F22" s="11" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C23" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E23" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="F23" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="F23" s="11" t="s">
-        <v>158</v>
-      </c>
       <c r="J23" s="11" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.25">
@@ -1701,13 +1701,13 @@
         <v>7</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.25">
@@ -1718,13 +1718,13 @@
         <v>9</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.25">
@@ -1735,13 +1735,13 @@
         <v>11</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.25">
@@ -1752,16 +1752,16 @@
         <v>13</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="J27" s="11" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.25">
@@ -1772,19 +1772,19 @@
         <v>19</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F28" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="J28" s="12" t="s">
         <v>232</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="J28" s="12" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.25">
@@ -1795,16 +1795,16 @@
         <v>23</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J29" s="12" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.25">
@@ -1815,16 +1815,16 @@
         <v>31</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E30" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="F30" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="F30" s="11" t="s">
-        <v>171</v>
-      </c>
       <c r="J30" s="11" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.25">
@@ -1835,7 +1835,7 @@
         <v>39</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E31" s="14"/>
     </row>
@@ -1847,7 +1847,7 @@
         <v>40</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E32" s="14"/>
     </row>
@@ -1859,10 +1859,10 @@
         <v>41</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.25">
@@ -1873,7 +1873,7 @@
         <v>42</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E34" s="14"/>
     </row>
@@ -1885,7 +1885,7 @@
         <v>43</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E35" s="14"/>
     </row>
@@ -1897,7 +1897,7 @@
         <v>44</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E36" s="14"/>
     </row>
@@ -1909,7 +1909,7 @@
         <v>45</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E37" s="14"/>
     </row>
@@ -1921,7 +1921,7 @@
         <v>47</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E38" s="14"/>
     </row>
@@ -1933,7 +1933,7 @@
         <v>49</v>
       </c>
       <c r="D39" s="15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E39" s="14"/>
     </row>
@@ -1945,7 +1945,7 @@
         <v>51</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E40" s="14"/>
     </row>
@@ -1957,16 +1957,16 @@
         <v>55</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J41" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="42" spans="2:10" x14ac:dyDescent="0.25">
@@ -1977,16 +1977,16 @@
         <v>56</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J42" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.25">
@@ -1997,13 +1997,13 @@
         <v>57</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E43" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="F43" s="11" t="s">
         <v>174</v>
-      </c>
-      <c r="F43" s="11" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.25">
@@ -2014,16 +2014,16 @@
         <v>58</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J44" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="45" spans="2:10" x14ac:dyDescent="0.25">
@@ -2034,16 +2034,16 @@
         <v>59</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J45" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="46" spans="2:10" x14ac:dyDescent="0.25">
@@ -2054,16 +2054,16 @@
         <v>62</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J46" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.25">
@@ -2074,16 +2074,16 @@
         <v>64</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J47" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.25">
@@ -2094,16 +2094,16 @@
         <v>65</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J48" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="49" spans="2:10" x14ac:dyDescent="0.25">
@@ -2114,253 +2114,253 @@
         <v>66</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J49" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50" s="16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J50" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51" s="16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C51" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J51" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B52" s="16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C52" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J52" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="53" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B53" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C53" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54" s="16" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C54" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J54" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B55" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="C55" t="s">
         <v>107</v>
       </c>
-      <c r="C55" t="s">
-        <v>108</v>
-      </c>
       <c r="D55" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E55" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="F55" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="F55" s="11" t="s">
-        <v>191</v>
-      </c>
       <c r="J55" s="11" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="56" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B56" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="C56" t="s">
+        <v>108</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="E56" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="C56" t="s">
-        <v>109</v>
-      </c>
-      <c r="D56" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="E56" s="11" t="s">
-        <v>193</v>
-      </c>
       <c r="F56" s="11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J56" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="57" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B57" s="16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C57" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J57" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="58" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B58" s="16" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C58" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E58" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="F58" s="11" t="s">
         <v>195</v>
       </c>
-      <c r="F58" s="11" t="s">
-        <v>196</v>
-      </c>
       <c r="J58" s="11" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="59" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B59" s="16" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C59" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E59" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="F59" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="F59" s="11" t="s">
-        <v>198</v>
-      </c>
       <c r="J59" s="11" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="60" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B60" s="16" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C60" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E60" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="F60" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="F60" s="11" t="s">
-        <v>200</v>
-      </c>
       <c r="J60" s="11" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="61" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B61" s="16" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C61" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J61" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="62" spans="2:10" x14ac:dyDescent="0.25">
@@ -2371,176 +2371,176 @@
         <v>70</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J62" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="63" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B63" s="17" t="s">
+        <v>220</v>
+      </c>
+      <c r="C63" t="s">
+        <v>202</v>
+      </c>
+      <c r="D63" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="E63" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="C63" t="s">
-        <v>203</v>
-      </c>
-      <c r="D63" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="E63" s="11" t="s">
-        <v>222</v>
-      </c>
       <c r="F63" s="11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="64" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B64" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="C64" t="s">
+        <v>203</v>
+      </c>
+      <c r="D64" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="E64" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="C64" t="s">
-        <v>204</v>
-      </c>
-      <c r="D64" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="E64" s="11" t="s">
-        <v>220</v>
-      </c>
       <c r="F64" s="11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J64" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="65" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B65" s="17" t="s">
+        <v>224</v>
+      </c>
+      <c r="C65" t="s">
+        <v>204</v>
+      </c>
+      <c r="D65" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="E65" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="C65" t="s">
-        <v>205</v>
-      </c>
-      <c r="D65" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="E65" s="11" t="s">
-        <v>226</v>
-      </c>
       <c r="F65" s="11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="66" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B66" s="17" t="s">
+        <v>209</v>
+      </c>
+      <c r="C66" t="s">
+        <v>205</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="E66" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="C66" t="s">
-        <v>206</v>
-      </c>
-      <c r="D66" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="E66" s="11" t="s">
-        <v>211</v>
-      </c>
       <c r="F66" s="11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="67" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B67" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="C67" t="s">
+        <v>206</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="E67" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="C67" t="s">
-        <v>207</v>
-      </c>
-      <c r="D67" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="E67" s="11" t="s">
-        <v>218</v>
-      </c>
       <c r="F67" s="11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J67" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="68" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B68" s="17" t="s">
+        <v>222</v>
+      </c>
+      <c r="C68" t="s">
+        <v>207</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="E68" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="C68" t="s">
-        <v>208</v>
-      </c>
-      <c r="D68" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="E68" s="11" t="s">
-        <v>224</v>
-      </c>
       <c r="F68" s="11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="69" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B69" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="C69" t="s">
+        <v>208</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="E69" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="C69" t="s">
-        <v>209</v>
-      </c>
-      <c r="D69" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="E69" s="11" t="s">
-        <v>216</v>
-      </c>
       <c r="F69" s="11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="70" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B70" s="17" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C70" t="s">
+        <v>211</v>
+      </c>
+      <c r="D70" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="E70" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="D70" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="E70" s="11" t="s">
-        <v>213</v>
-      </c>
       <c r="F70" s="11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J70" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>

--- a/NHIS variable list REVISED 6-14-24_Now_Moddified new.xlsx
+++ b/NHIS variable list REVISED 6-14-24_Now_Moddified new.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ncaandt-my.sharepoint.com/personal/hmoradi_ncat_edu/Documents/06_Codes/NHIS-surf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{1CD7837E-75C9-5E40-80AC-B4DD76B197DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B7E2BCA-6C1E-4F1F-B0E5-E75077A43D0E}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{1CD7837E-75C9-5E40-80AC-B4DD76B197DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA7810B7-B88D-40D1-BFCA-DE69673EFB5B}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AA949552-4F9F-40F0-90AF-3F34A678AD64}"/>
   </bookViews>
@@ -447,9 +447,6 @@
     <t>1=yes;2=no</t>
   </si>
   <si>
-    <t>Body Mass Inxex Category</t>
-  </si>
-  <si>
     <t>Ever Had Anxiety Disorder</t>
   </si>
   <si>
@@ -552,9 +549,6 @@
     <t>1=very worried; 2=somewhat worried; 3=not at all worried</t>
   </si>
   <si>
-    <t>Delayed Medicall Caure Due to Cost in Past 12 Months</t>
-  </si>
-  <si>
     <t>Problems Paying Medical Bills in Past 12 Months</t>
   </si>
   <si>
@@ -781,6 +775,12 @@
   </si>
   <si>
     <t>take medication for worried/nervous/anxious feelings</t>
+  </si>
+  <si>
+    <t>Body Mass Index Category</t>
+  </si>
+  <si>
+    <t>Delayed Medical Care Due to Cost in Past 12 Months</t>
   </si>
 </sst>
 </file>
@@ -1283,7 +1283,7 @@
         <v>129</v>
       </c>
       <c r="J1" s="10" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="2" spans="2:10" x14ac:dyDescent="0.25">
@@ -1314,10 +1314,10 @@
         <v>123</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J3" s="11" t="s">
         <v>133</v>
@@ -1334,10 +1334,10 @@
         <v>124</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.25">
@@ -1357,7 +1357,7 @@
         <v>136</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.25">
@@ -1388,13 +1388,13 @@
         <v>124</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.25">
@@ -1408,13 +1408,13 @@
         <v>124</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.25">
@@ -1428,13 +1428,13 @@
         <v>124</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.25">
@@ -1465,10 +1465,10 @@
         <v>134</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.25">
@@ -1482,13 +1482,13 @@
         <v>127</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>139</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.25">
@@ -1502,13 +1502,13 @@
         <v>127</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F13" s="11" t="s">
         <v>136</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.25">
@@ -1522,13 +1522,13 @@
         <v>125</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>140</v>
+        <v>250</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.25">
@@ -1542,10 +1542,10 @@
         <v>127</v>
       </c>
       <c r="E15" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="F15" s="11" t="s">
         <v>144</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.25">
@@ -1553,19 +1553,19 @@
         <v>73</v>
       </c>
       <c r="C16" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>127</v>
       </c>
       <c r="E16" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="F16" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="F16" s="11" t="s">
-        <v>147</v>
-      </c>
       <c r="J16" s="11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.25">
@@ -1579,10 +1579,10 @@
         <v>127</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.25">
@@ -1596,10 +1596,10 @@
         <v>127</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.25">
@@ -1613,13 +1613,13 @@
         <v>127</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J19" s="11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.25">
@@ -1633,10 +1633,10 @@
         <v>127</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.25">
@@ -1650,10 +1650,10 @@
         <v>127</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.25">
@@ -1667,10 +1667,10 @@
         <v>127</v>
       </c>
       <c r="E22" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="F22" s="11" t="s">
         <v>154</v>
-      </c>
-      <c r="F22" s="11" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.25">
@@ -1684,13 +1684,13 @@
         <v>125</v>
       </c>
       <c r="E23" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="F23" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="F23" s="11" t="s">
-        <v>157</v>
-      </c>
       <c r="J23" s="11" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.25">
@@ -1704,10 +1704,10 @@
         <v>126</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.25">
@@ -1721,10 +1721,10 @@
         <v>126</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.25">
@@ -1738,10 +1738,10 @@
         <v>126</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.25">
@@ -1755,13 +1755,13 @@
         <v>126</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J27" s="11" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.25">
@@ -1775,16 +1775,16 @@
         <v>126</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="J28" s="12" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.25">
@@ -1798,13 +1798,13 @@
         <v>126</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J29" s="12" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.25">
@@ -1818,13 +1818,13 @@
         <v>126</v>
       </c>
       <c r="E30" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="F30" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="F30" s="11" t="s">
-        <v>170</v>
-      </c>
       <c r="J30" s="11" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.25">
@@ -1862,7 +1862,7 @@
         <v>126</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.25">
@@ -1960,13 +1960,13 @@
         <v>126</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F41" s="11" t="s">
         <v>139</v>
       </c>
       <c r="J41" s="11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="42" spans="2:10" x14ac:dyDescent="0.25">
@@ -1980,13 +1980,13 @@
         <v>126</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F42" s="11" t="s">
         <v>139</v>
       </c>
       <c r="J42" s="11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.25">
@@ -2000,10 +2000,10 @@
         <v>126</v>
       </c>
       <c r="E43" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="F43" s="11" t="s">
         <v>173</v>
-      </c>
-      <c r="F43" s="11" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.25">
@@ -2017,13 +2017,13 @@
         <v>126</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>175</v>
+        <v>251</v>
       </c>
       <c r="F44" s="11" t="s">
         <v>139</v>
       </c>
       <c r="J44" s="11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="45" spans="2:10" x14ac:dyDescent="0.25">
@@ -2037,13 +2037,13 @@
         <v>126</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F45" s="11" t="s">
         <v>139</v>
       </c>
       <c r="J45" s="11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="46" spans="2:10" x14ac:dyDescent="0.25">
@@ -2057,13 +2057,13 @@
         <v>126</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F46" s="11" t="s">
         <v>139</v>
       </c>
       <c r="J46" s="11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.25">
@@ -2077,13 +2077,13 @@
         <v>126</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F47" s="11" t="s">
         <v>139</v>
       </c>
       <c r="J47" s="11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.25">
@@ -2097,13 +2097,13 @@
         <v>126</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F48" s="11" t="s">
         <v>139</v>
       </c>
       <c r="J48" s="11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="49" spans="2:10" x14ac:dyDescent="0.25">
@@ -2117,13 +2117,13 @@
         <v>126</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F49" s="11" t="s">
         <v>139</v>
       </c>
       <c r="J49" s="11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="50" spans="2:10" x14ac:dyDescent="0.25">
@@ -2137,13 +2137,13 @@
         <v>126</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F50" s="11" t="s">
         <v>139</v>
       </c>
       <c r="J50" s="11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="51" spans="2:10" x14ac:dyDescent="0.25">
@@ -2157,13 +2157,13 @@
         <v>126</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F51" s="11" t="s">
         <v>139</v>
       </c>
       <c r="J51" s="11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="52" spans="2:10" x14ac:dyDescent="0.25">
@@ -2177,13 +2177,13 @@
         <v>126</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F52" s="11" t="s">
         <v>139</v>
       </c>
       <c r="J52" s="11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="53" spans="2:10" x14ac:dyDescent="0.25">
@@ -2197,10 +2197,10 @@
         <v>126</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="54" spans="2:10" x14ac:dyDescent="0.25">
@@ -2214,13 +2214,13 @@
         <v>126</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F54" s="11" t="s">
         <v>139</v>
       </c>
       <c r="J54" s="11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="55" spans="2:10" x14ac:dyDescent="0.25">
@@ -2234,18 +2234,18 @@
         <v>126</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="J55" s="11" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="56" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B56" s="16" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C56" t="s">
         <v>108</v>
@@ -2254,13 +2254,13 @@
         <v>126</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F56" s="11" t="s">
         <v>139</v>
       </c>
       <c r="J56" s="11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="57" spans="2:10" x14ac:dyDescent="0.25">
@@ -2274,13 +2274,13 @@
         <v>126</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F57" s="11" t="s">
         <v>139</v>
       </c>
       <c r="J57" s="11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="58" spans="2:10" x14ac:dyDescent="0.25">
@@ -2294,13 +2294,13 @@
         <v>126</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="J58" s="11" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="59" spans="2:10" x14ac:dyDescent="0.25">
@@ -2314,13 +2314,13 @@
         <v>126</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="J59" s="11" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="60" spans="2:10" x14ac:dyDescent="0.25">
@@ -2334,13 +2334,13 @@
         <v>126</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="J60" s="11" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="61" spans="2:10" x14ac:dyDescent="0.25">
@@ -2354,13 +2354,13 @@
         <v>126</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F61" s="11" t="s">
         <v>139</v>
       </c>
       <c r="J61" s="11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="62" spans="2:10" x14ac:dyDescent="0.25">
@@ -2374,173 +2374,173 @@
         <v>125</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F62" s="11" t="s">
         <v>139</v>
       </c>
       <c r="J62" s="11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="63" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B63" s="17" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C63" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D63" s="8" t="s">
         <v>125</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F63" s="11" t="s">
         <v>136</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="64" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B64" s="17" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C64" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D64" s="8" t="s">
         <v>125</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F64" s="11" t="s">
         <v>136</v>
       </c>
       <c r="J64" s="11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="65" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B65" s="17" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C65" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D65" s="8" t="s">
         <v>125</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F65" s="11" t="s">
         <v>136</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="66" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B66" s="17" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C66" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D66" s="8" t="s">
         <v>125</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F66" s="11" t="s">
         <v>136</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="67" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B67" s="17" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C67" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D67" s="8" t="s">
         <v>125</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F67" s="11" t="s">
         <v>136</v>
       </c>
       <c r="J67" s="11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="68" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B68" s="17" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C68" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D68" s="8" t="s">
         <v>125</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F68" s="11" t="s">
         <v>136</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="69" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B69" s="17" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C69" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D69" s="8" t="s">
         <v>125</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F69" s="11" t="s">
         <v>136</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="70" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B70" s="17" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C70" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D70" s="8" t="s">
         <v>125</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F70" s="11" t="s">
         <v>136</v>
       </c>
       <c r="J70" s="11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>
